--- a/data/Data trimestral 1950 a 2023 PRUEBA (promedios anuales).xlsx
+++ b/data/Data trimestral 1950 a 2023 PRUEBA (promedios anuales).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mariana/Library/CloudStorage/GoogleDrive-marianabarrenadrive@gmail.com/Mi unidad/TESIS UCA/UCA Proyecto de TESIS/Estadísticas/Github/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06EFD12C-5A04-8E4D-8AF6-2E4F3A31572E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89035412-09C7-C641-A336-A999D967B02D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17180" xr2:uid="{081104FB-1F73-C945-9C9A-B52E522B90FE}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Ebc</t>
   </si>
@@ -59,12 +59,6 @@
   </si>
   <si>
     <t>año</t>
-  </si>
-  <si>
-    <t>trimestre</t>
-  </si>
-  <si>
-    <t>4ºTr</t>
   </si>
   <si>
     <t>pbird</t>
@@ -117,16 +111,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -449,2662 +440,2432 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D748D8A8-3F83-DF4A-8DE1-BB2B913EFB46}">
-  <dimension ref="A1:L379"/>
+  <dimension ref="A1:K379"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="7.6640625" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>10</v>
+      <c r="F1" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>1950</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>9</v>
+      <c r="B2">
+        <v>3.4745696411495382E-12</v>
       </c>
       <c r="C2">
-        <v>3.4745696411495382E-12</v>
+        <v>1.0723825000000002E-12</v>
       </c>
       <c r="D2">
         <v>1.0723825000000002E-12</v>
       </c>
       <c r="E2">
-        <v>1.0723825000000002E-12</v>
-      </c>
-      <c r="F2">
         <v>142105.75</v>
       </c>
+      <c r="G2">
+        <v>2.4458333333333333</v>
+      </c>
       <c r="H2">
-        <v>2.4458333333333333</v>
+        <v>1.3308333333333333</v>
       </c>
       <c r="I2">
-        <v>1.3308333333333333</v>
-      </c>
-      <c r="J2">
         <v>1.9808333333333334</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>1951</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>9</v>
+      <c r="B3">
+        <v>4.7488405092829602E-12</v>
       </c>
       <c r="C3">
-        <v>4.7488405092829602E-12</v>
+        <v>1.4195825000000001E-12</v>
       </c>
       <c r="D3">
         <v>1.4195825000000001E-12</v>
       </c>
       <c r="E3">
-        <v>1.4195825000000001E-12</v>
-      </c>
-      <c r="F3">
         <v>147447.5</v>
       </c>
+      <c r="G3">
+        <v>2.8908333333333336</v>
+      </c>
       <c r="H3">
-        <v>2.8908333333333336</v>
+        <v>1.6233333333333335</v>
       </c>
       <c r="I3">
-        <v>1.6233333333333335</v>
-      </c>
-      <c r="J3">
         <v>2.1191666666666666</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>1952</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>9</v>
+      <c r="B4">
+        <v>6.5878064103641582E-12</v>
       </c>
       <c r="C4">
-        <v>6.5878064103641582E-12</v>
+        <v>1.4031708333333334E-12</v>
       </c>
       <c r="D4">
         <v>1.4031708333333334E-12</v>
       </c>
       <c r="E4">
-        <v>1.4031708333333334E-12</v>
-      </c>
-      <c r="F4">
         <v>140518</v>
       </c>
+      <c r="G4">
+        <v>2.8233333333333328</v>
+      </c>
       <c r="H4">
-        <v>2.8233333333333328</v>
+        <v>1.645</v>
       </c>
       <c r="I4">
-        <v>1.645</v>
-      </c>
-      <c r="J4">
         <v>2.1150000000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>1953</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>9</v>
+      <c r="B5">
+        <v>6.8493627381600992E-12</v>
       </c>
       <c r="C5">
-        <v>6.8493627381600992E-12</v>
+        <v>1.3975000000000003E-12</v>
       </c>
       <c r="D5">
         <v>1.3975000000000003E-12</v>
       </c>
       <c r="E5">
-        <v>1.3975000000000003E-12</v>
-      </c>
-      <c r="F5">
         <v>147325</v>
       </c>
+      <c r="G5">
+        <v>2.6141666666666672</v>
+      </c>
       <c r="H5">
-        <v>2.6141666666666672</v>
+        <v>1.4425000000000001</v>
       </c>
       <c r="I5">
-        <v>1.4425000000000001</v>
-      </c>
-      <c r="J5">
         <v>1.9891666666666667</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>1954</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>9</v>
+      <c r="B6">
+        <v>7.1092866062125048E-12</v>
       </c>
       <c r="C6">
-        <v>7.1092866062125048E-12</v>
+        <v>1.3975200000000003E-12</v>
       </c>
       <c r="D6">
         <v>1.3975200000000003E-12</v>
       </c>
       <c r="E6">
-        <v>1.3975200000000003E-12</v>
-      </c>
-      <c r="F6">
         <v>153323.75</v>
       </c>
+      <c r="G6">
+        <v>3.039166666666667</v>
+      </c>
       <c r="H6">
-        <v>3.039166666666667</v>
+        <v>1.4558333333333333</v>
       </c>
       <c r="I6">
-        <v>1.4558333333333333</v>
-      </c>
-      <c r="J6">
         <v>2.0475000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>1955</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
+      <c r="B7">
+        <v>7.9851919508217778E-12</v>
       </c>
       <c r="C7">
-        <v>7.9851919508217778E-12</v>
+        <v>1.7356916666666671E-12</v>
       </c>
       <c r="D7">
         <v>1.7356916666666671E-12</v>
       </c>
       <c r="E7">
-        <v>1.7356916666666671E-12</v>
-      </c>
-      <c r="F7">
         <v>163917.75</v>
       </c>
+      <c r="G7">
+        <v>2.2925</v>
+      </c>
       <c r="H7">
-        <v>2.2925</v>
+        <v>1.3033333333333335</v>
       </c>
       <c r="I7">
-        <v>1.3033333333333335</v>
-      </c>
-      <c r="J7">
         <v>2.0241666666666664</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>1956</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
+      <c r="B8">
+        <v>9.0562215808863041E-12</v>
       </c>
       <c r="C8">
-        <v>9.0562215808863041E-12</v>
+        <v>3.5774166666666671E-12</v>
       </c>
       <c r="D8">
         <v>3.5774166666666671E-12</v>
       </c>
       <c r="E8">
-        <v>3.5774166666666671E-12</v>
-      </c>
-      <c r="F8">
         <v>168624.5</v>
       </c>
+      <c r="G8">
+        <v>2.3983333333333334</v>
+      </c>
       <c r="H8">
-        <v>2.3983333333333334</v>
+        <v>1.3</v>
       </c>
       <c r="I8">
-        <v>1.3</v>
-      </c>
-      <c r="J8">
         <v>1.9758333333333333</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>1957</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
+      <c r="B9">
+        <v>1.1293930889691559E-11</v>
       </c>
       <c r="C9">
-        <v>1.1293930889691559E-11</v>
+        <v>4.0200000000000002E-12</v>
       </c>
       <c r="D9">
         <v>4.0200000000000002E-12</v>
       </c>
       <c r="E9">
-        <v>4.0200000000000002E-12</v>
+        <v>177382.75</v>
       </c>
       <c r="F9">
-        <v>177382.75</v>
+        <v>14.212204605588674</v>
       </c>
       <c r="G9">
-        <v>14.212204605588674</v>
+        <v>2.1875</v>
       </c>
       <c r="H9">
-        <v>2.1875</v>
+        <v>1.1599166666666667</v>
       </c>
       <c r="I9">
-        <v>1.1599166666666667</v>
-      </c>
-      <c r="J9">
         <v>1.9724999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>1958</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
+      <c r="B10">
+        <v>1.4861444928646048E-11</v>
       </c>
       <c r="C10">
-        <v>1.4861444928646048E-11</v>
+        <v>4.8000833333333343E-12</v>
       </c>
       <c r="D10">
         <v>4.8000833333333343E-12</v>
       </c>
       <c r="E10">
-        <v>4.8000833333333343E-12</v>
+        <v>188141.5</v>
       </c>
       <c r="F10">
-        <v>188141.5</v>
+        <v>13.560490712012449</v>
       </c>
       <c r="G10">
-        <v>13.560490712012449</v>
+        <v>2.0508333333333333</v>
       </c>
       <c r="H10">
-        <v>2.0508333333333333</v>
+        <v>1.0700833333333333</v>
       </c>
       <c r="I10">
-        <v>1.0700833333333333</v>
-      </c>
-      <c r="J10">
         <v>1.7933333333333332</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>1959</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
+      <c r="B11">
+        <v>3.1757796273700329E-11</v>
       </c>
       <c r="C11">
-        <v>3.1757796273700329E-11</v>
+        <v>7.9920833332749996E-12</v>
       </c>
       <c r="D11">
-        <v>7.9920833332749996E-12</v>
+        <v>7.9190833333333343E-12</v>
       </c>
       <c r="E11">
-        <v>7.9190833333333343E-12</v>
+        <v>176120.25</v>
       </c>
       <c r="F11">
-        <v>176120.25</v>
+        <v>13.311061996808199</v>
       </c>
       <c r="G11">
-        <v>13.311061996808199</v>
+        <v>2.0250000000000004</v>
       </c>
       <c r="H11">
-        <v>2.0250000000000004</v>
+        <v>1.0739166666666666</v>
       </c>
       <c r="I11">
-        <v>1.0739166666666666</v>
-      </c>
-      <c r="J11">
         <v>1.7458333333333333</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:11">
       <c r="A12">
         <v>1960</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
+      <c r="B12">
+        <v>4.0213801706849175E-11</v>
       </c>
       <c r="C12">
-        <v>4.0213801706849175E-11</v>
+        <v>8.2889999999750011E-12</v>
       </c>
       <c r="D12">
-        <v>8.2889999999750011E-12</v>
+        <v>8.2940833333333362E-12</v>
       </c>
       <c r="E12">
-        <v>8.2940833333333362E-12</v>
+        <v>190032</v>
       </c>
       <c r="F12">
-        <v>190032</v>
+        <v>13.483202941044725</v>
       </c>
       <c r="G12">
-        <v>13.483202941044725</v>
+        <v>1.9833333333333332</v>
       </c>
       <c r="H12">
-        <v>1.9833333333333332</v>
+        <v>1.0243333333333335</v>
       </c>
       <c r="I12">
-        <v>1.0243333333333335</v>
-      </c>
-      <c r="J12">
         <v>1.7608333333333335</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:11">
       <c r="A13">
         <v>1961</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
+      <c r="B13">
+        <v>4.573269463866821E-11</v>
       </c>
       <c r="C13">
-        <v>4.573269463866821E-11</v>
+        <v>8.2855833332666656E-12</v>
       </c>
       <c r="D13">
-        <v>8.2855833332666656E-12</v>
+        <v>8.2830833333333355E-12</v>
       </c>
       <c r="E13">
-        <v>8.2830833333333355E-12</v>
+        <v>203568.75</v>
       </c>
       <c r="F13">
-        <v>203568.75</v>
+        <v>13.30052275528705</v>
       </c>
       <c r="G13">
-        <v>13.30052275528705</v>
+        <v>2.5041666666666664</v>
       </c>
       <c r="H13">
-        <v>2.5041666666666664</v>
+        <v>1.012</v>
       </c>
       <c r="I13">
-        <v>1.012</v>
-      </c>
-      <c r="J13">
         <v>1.8083333333333331</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:11">
       <c r="A14">
         <v>1962</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>9</v>
+      <c r="B14">
+        <v>5.7681000039625438E-11</v>
       </c>
       <c r="C14">
-        <v>5.7681000039625438E-11</v>
+        <v>1.1832833333287499E-11</v>
       </c>
       <c r="D14">
-        <v>1.1832833333287499E-11</v>
+        <v>1.1372583333333335E-11</v>
       </c>
       <c r="E14">
-        <v>1.1372583333333335E-11</v>
+        <v>200420.25</v>
       </c>
       <c r="F14">
-        <v>200420.25</v>
+        <v>13.015963235199624</v>
       </c>
       <c r="G14">
-        <v>13.015963235199624</v>
+        <v>2.3224999999999998</v>
       </c>
       <c r="H14">
-        <v>2.3224999999999998</v>
+        <v>1.0221666666666667</v>
       </c>
       <c r="I14">
-        <v>1.0221666666666667</v>
-      </c>
-      <c r="J14">
         <v>1.9583333333333333</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:11">
       <c r="A15">
         <v>1963</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>9</v>
+      <c r="B15">
+        <v>7.2663670219596274E-11</v>
       </c>
       <c r="C15">
-        <v>7.2663670219596274E-11</v>
+        <v>1.3871666666625E-11</v>
       </c>
       <c r="D15">
-        <v>1.3871666666625E-11</v>
+        <v>1.382941666666667E-11</v>
       </c>
       <c r="E15">
-        <v>1.382941666666667E-11</v>
+        <v>195924</v>
       </c>
       <c r="F15">
-        <v>195924</v>
+        <v>13.096764086592451</v>
       </c>
       <c r="G15">
-        <v>13.096764086592451</v>
+        <v>2.4958333333333331</v>
       </c>
       <c r="H15">
-        <v>2.4958333333333331</v>
+        <v>1.1224999999999998</v>
       </c>
       <c r="I15">
-        <v>1.1224999999999998</v>
-      </c>
-      <c r="J15">
         <v>1.9400000000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:11">
       <c r="A16">
         <v>1964</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>9</v>
+      <c r="B16">
+        <v>8.8754553834900743E-11</v>
       </c>
       <c r="C16">
-        <v>8.8754553834900743E-11</v>
+        <v>1.4039166666616675E-11</v>
       </c>
       <c r="D16">
-        <v>1.4039166666616675E-11</v>
+        <v>1.3988083333333335E-11</v>
       </c>
       <c r="E16">
-        <v>1.3988083333333335E-11</v>
+        <v>215620.25</v>
       </c>
       <c r="F16">
-        <v>215620.25</v>
+        <v>13.490229101965125</v>
       </c>
       <c r="G16">
-        <v>13.490229101965125</v>
+        <v>2.4966666666666666</v>
       </c>
       <c r="H16">
-        <v>2.4966666666666666</v>
+        <v>1.1341666666666668</v>
       </c>
       <c r="I16">
-        <v>1.1341666666666668</v>
-      </c>
-      <c r="J16">
         <v>1.6016666666666666</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:11">
       <c r="A17">
         <v>1965</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>9</v>
+      <c r="B17">
+        <v>1.1413410316012789E-10</v>
       </c>
       <c r="C17">
-        <v>1.1413410316012789E-10</v>
+        <v>1.6956666666641651E-11</v>
       </c>
       <c r="D17">
-        <v>1.6956666666641651E-11</v>
+        <v>1.6849333333333335E-11</v>
       </c>
       <c r="E17">
-        <v>1.6849333333333335E-11</v>
+        <v>234895</v>
       </c>
       <c r="F17">
-        <v>234895</v>
+        <v>13.56400379243755</v>
       </c>
       <c r="G17">
-        <v>13.56400379243755</v>
+        <v>2.6183333333333332</v>
       </c>
       <c r="H17">
-        <v>2.6183333333333332</v>
+        <v>1.1816666666666666</v>
       </c>
       <c r="I17">
-        <v>1.1816666666666666</v>
-      </c>
-      <c r="J17">
         <v>1.3475000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:11">
       <c r="A18">
         <v>1966</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>9</v>
+      <c r="B18">
+        <v>1.5050117975040785E-10</v>
       </c>
       <c r="C18">
-        <v>1.5050117975040785E-10</v>
+        <v>2.0914999999966651E-11</v>
       </c>
       <c r="D18">
-        <v>2.0914999999966651E-11</v>
+        <v>2.0744750000000003E-11</v>
       </c>
       <c r="E18">
-        <v>2.0744750000000003E-11</v>
+        <v>236864.75</v>
       </c>
       <c r="F18">
-        <v>236864.75</v>
+        <v>13.929364163988051</v>
       </c>
       <c r="G18">
-        <v>13.929364163988051</v>
+        <v>2.9250000000000003</v>
       </c>
       <c r="H18">
-        <v>2.9250000000000003</v>
+        <v>1.2466666666666668</v>
       </c>
       <c r="I18">
-        <v>1.2466666666666668</v>
-      </c>
-      <c r="J18">
         <v>1.551666666666667</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:11">
       <c r="A19">
         <v>1967</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>9</v>
+      <c r="B19">
+        <v>1.9447810347344265E-10</v>
       </c>
       <c r="C19">
-        <v>1.9447810347344265E-10</v>
+        <v>3.3342499999991677E-11</v>
       </c>
       <c r="D19">
-        <v>3.3342499999991677E-11</v>
+        <v>3.3113250000000005E-11</v>
       </c>
       <c r="E19">
-        <v>3.3113250000000005E-11</v>
+        <v>243536.25</v>
       </c>
       <c r="F19">
-        <v>243536.25</v>
+        <v>14.052321981324926</v>
       </c>
       <c r="G19">
-        <v>14.052321981324926</v>
+        <v>2.6191666666666666</v>
       </c>
       <c r="H19">
-        <v>2.6191666666666666</v>
+        <v>1.1729166666666666</v>
       </c>
       <c r="I19">
-        <v>1.1729166666666666</v>
-      </c>
-      <c r="J19">
         <v>1.4708333333333332</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:11">
       <c r="A20">
         <v>1968</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>9</v>
+      <c r="B20">
+        <v>2.2603672454306483E-10</v>
       </c>
       <c r="C20">
-        <v>2.2603672454306483E-10</v>
+        <v>3.5000000000000002E-11</v>
       </c>
       <c r="D20">
-        <v>3.5000000000000002E-11</v>
+        <v>3.5000000000000008E-11</v>
       </c>
       <c r="E20">
-        <v>3.5000000000000008E-11</v>
+        <v>254633.25</v>
       </c>
       <c r="F20">
-        <v>254633.25</v>
+        <v>14.213923684145724</v>
       </c>
       <c r="G20">
-        <v>14.213923684145724</v>
+        <v>2.4933333333333332</v>
       </c>
       <c r="H20">
-        <v>2.4933333333333332</v>
+        <v>1.0389999999999999</v>
       </c>
       <c r="I20">
-        <v>1.0389999999999999</v>
-      </c>
-      <c r="J20">
         <v>1.3008333333333333</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:11">
       <c r="A21">
         <v>1969</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>9</v>
+      <c r="B21">
+        <v>2.4316591301672354E-10</v>
       </c>
       <c r="C21">
-        <v>2.4316591301672354E-10</v>
+        <v>3.5000000000000002E-11</v>
       </c>
       <c r="D21">
-        <v>3.5000000000000002E-11</v>
+        <v>3.5000000000000008E-11</v>
       </c>
       <c r="E21">
-        <v>3.5000000000000008E-11</v>
+        <v>275881</v>
       </c>
       <c r="F21">
-        <v>275881</v>
+        <v>14.629940020623625</v>
       </c>
       <c r="G21">
-        <v>14.629940020623625</v>
+        <v>2.4291666666666663</v>
       </c>
       <c r="H21">
-        <v>2.4291666666666663</v>
+        <v>1.1283333333333334</v>
       </c>
       <c r="I21">
-        <v>1.1283333333333334</v>
-      </c>
-      <c r="J21">
         <v>1.2549999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:11">
       <c r="A22">
         <v>1970</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>9</v>
+      <c r="B22">
+        <v>2.7618422517368117E-10</v>
       </c>
       <c r="C22">
-        <v>2.7618422517368117E-10</v>
+        <v>3.7916666656666672E-11</v>
       </c>
       <c r="D22">
-        <v>3.7916666656666672E-11</v>
+        <v>3.7916666666666665E-11</v>
       </c>
       <c r="E22">
-        <v>3.7916666666666665E-11</v>
+        <v>290069.75</v>
       </c>
       <c r="F22">
-        <v>290069.75</v>
+        <v>15.630009007273875</v>
       </c>
       <c r="G22">
-        <v>15.630009007273875</v>
+        <v>2.6008333333333336</v>
       </c>
       <c r="H22">
-        <v>2.6008333333333336</v>
+        <v>1.2341666666666666</v>
       </c>
       <c r="I22">
-        <v>1.2341666666666666</v>
-      </c>
-      <c r="J22">
         <v>1.3308333333333333</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:11">
       <c r="A23">
         <v>1971</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>9</v>
+      <c r="B23">
+        <v>3.7208458434387189E-10</v>
       </c>
       <c r="C23">
-        <v>3.7208458434387189E-10</v>
+        <v>4.5216666656666675E-11</v>
       </c>
       <c r="D23">
-        <v>4.5216666656666675E-11</v>
+        <v>5.4175000000000009E-11</v>
       </c>
       <c r="E23">
-        <v>5.4175000000000009E-11</v>
+        <v>300804.5</v>
       </c>
       <c r="F23">
-        <v>300804.5</v>
+        <v>16.438240861454727</v>
       </c>
       <c r="G23">
-        <v>16.438240861454727</v>
+        <v>2.9391666666666665</v>
       </c>
       <c r="H23">
-        <v>2.9391666666666665</v>
+        <v>1.2678333333333331</v>
       </c>
       <c r="I23">
-        <v>1.2678333333333331</v>
-      </c>
-      <c r="J23">
         <v>1.3599999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:11">
       <c r="A24">
         <v>1972</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>9</v>
+      <c r="B24">
+        <v>5.8958581173349902E-10</v>
       </c>
       <c r="C24">
-        <v>5.8958581173349902E-10</v>
+        <v>4.9999999990000002E-11</v>
       </c>
       <c r="D24">
-        <v>4.9999999990000002E-11</v>
+        <v>9.8833333333333341E-11</v>
       </c>
       <c r="E24">
-        <v>9.8833333333333341E-11</v>
+        <v>306840</v>
       </c>
       <c r="F24">
-        <v>306840</v>
+        <v>17.633291851947924</v>
       </c>
       <c r="G24">
-        <v>17.633291851947924</v>
+        <v>3.2983333333333333</v>
       </c>
       <c r="H24">
-        <v>3.2983333333333333</v>
+        <v>1.1675</v>
       </c>
       <c r="I24">
-        <v>1.1675</v>
-      </c>
-      <c r="J24">
         <v>1.5733333333333335</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:11">
       <c r="A25">
         <v>1973</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>9</v>
+      <c r="B25">
+        <v>9.4512450965466199E-10</v>
       </c>
       <c r="C25">
-        <v>9.4512450965466199E-10</v>
+        <v>4.9999999990000002E-11</v>
       </c>
       <c r="D25">
-        <v>4.9999999990000002E-11</v>
+        <v>9.980000000000002E-11</v>
       </c>
       <c r="E25">
-        <v>9.980000000000002E-11</v>
+        <v>317959.5</v>
       </c>
       <c r="F25">
-        <v>317959.5</v>
+        <v>20.954275657195375</v>
       </c>
       <c r="G25">
-        <v>20.954275657195375</v>
+        <v>6.496666666666667</v>
       </c>
       <c r="H25">
-        <v>6.496666666666667</v>
+        <v>1.8941666666666666</v>
       </c>
       <c r="I25">
-        <v>1.8941666666666666</v>
-      </c>
-      <c r="J25">
         <v>3.1566666666666663</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:11">
       <c r="A26">
         <v>1974</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>9</v>
+      <c r="B26">
+        <v>1.1740000514609808E-9</v>
       </c>
       <c r="C26">
-        <v>1.1740000514609808E-9</v>
+        <v>4.9999999990000002E-11</v>
       </c>
       <c r="D26">
-        <v>4.9999999990000002E-11</v>
+        <v>9.980000000000002E-11</v>
       </c>
       <c r="E26">
-        <v>9.980000000000002E-11</v>
+        <v>337419.5</v>
       </c>
       <c r="F26">
-        <v>337419.5</v>
+        <v>31.033587300993851</v>
       </c>
       <c r="G26">
-        <v>31.033587300993851</v>
+        <v>6.4175000000000004</v>
       </c>
       <c r="H26">
-        <v>6.4175000000000004</v>
+        <v>2.9233333333333329</v>
       </c>
       <c r="I26">
-        <v>2.9233333333333329</v>
-      </c>
-      <c r="J26">
         <v>4.4841666666666669</v>
       </c>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:11">
       <c r="A27">
         <v>1975</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>9</v>
+      <c r="B27">
+        <v>3.3199847726584972E-9</v>
       </c>
       <c r="C27">
-        <v>3.3199847726584972E-9</v>
+        <v>3.6574999999500001E-10</v>
       </c>
       <c r="D27">
-        <v>3.6574999999500001E-10</v>
+        <v>4.0969166666666671E-10</v>
       </c>
       <c r="E27">
-        <v>4.0969166666666671E-10</v>
+        <v>334074.5</v>
       </c>
       <c r="F27">
-        <v>334074.5</v>
+        <v>33.826232773745524</v>
       </c>
       <c r="G27">
-        <v>33.826232773745524</v>
+        <v>5.24</v>
       </c>
       <c r="H27">
-        <v>5.24</v>
+        <v>2.6974999999999998</v>
       </c>
       <c r="I27">
-        <v>2.6974999999999998</v>
-      </c>
-      <c r="J27">
         <v>3.6775000000000002</v>
       </c>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:11">
       <c r="A28">
         <v>1976</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>9</v>
+      <c r="B28">
+        <v>1.8061141602795547E-8</v>
       </c>
       <c r="C28">
-        <v>1.8061141602795547E-8</v>
+        <v>1.3998333333316675E-9</v>
       </c>
       <c r="D28">
-        <v>1.3998333333316675E-9</v>
+        <v>2.5145833333333335E-9</v>
       </c>
       <c r="E28">
-        <v>2.5145833333333335E-9</v>
+        <v>331152.75</v>
       </c>
       <c r="F28">
-        <v>331152.75</v>
+        <v>34.860895341889076</v>
       </c>
       <c r="G28">
-        <v>34.860895341889076</v>
+        <v>5.5825000000000005</v>
       </c>
       <c r="H28">
-        <v>5.5825000000000005</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="I28">
-        <v>2.4900000000000002</v>
-      </c>
-      <c r="J28">
         <v>3.1458333333333335</v>
       </c>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:11">
       <c r="A29">
         <v>1977</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>9</v>
+      <c r="B29">
+        <v>4.9854489222021501E-8</v>
       </c>
       <c r="C29">
-        <v>4.9854489222021501E-8</v>
+        <v>4.0763333333283327E-9</v>
       </c>
       <c r="D29">
-        <v>4.0763333333283327E-9</v>
+        <v>4.2308333333333337E-9</v>
       </c>
       <c r="E29">
-        <v>4.2308333333333337E-9</v>
+        <v>354395.25</v>
       </c>
       <c r="F29">
-        <v>354395.25</v>
+        <v>37.634671588317353</v>
       </c>
       <c r="G29">
-        <v>37.634671588317353</v>
+        <v>6.8216666666666663</v>
       </c>
       <c r="H29">
-        <v>6.8216666666666663</v>
+        <v>2.0283333333333333</v>
       </c>
       <c r="I29">
-        <v>2.0283333333333333</v>
-      </c>
-      <c r="J29">
         <v>2.29</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:11">
       <c r="A30">
         <v>1978</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>9</v>
+      <c r="B30">
+        <v>1.3735350012973534E-7</v>
       </c>
       <c r="C30">
-        <v>1.3735350012973534E-7</v>
+        <v>7.9574999999958329E-9</v>
       </c>
       <c r="D30">
-        <v>7.9574999999958329E-9</v>
+        <v>8.1466666666666675E-9</v>
       </c>
       <c r="E30">
-        <v>8.1466666666666675E-9</v>
+        <v>339595.75</v>
       </c>
       <c r="F30">
-        <v>339595.75</v>
+        <v>40.917916941169523</v>
       </c>
       <c r="G30">
-        <v>40.917916941169523</v>
+        <v>6.2833333333333332</v>
       </c>
       <c r="H30">
-        <v>6.2833333333333332</v>
+        <v>2.101666666666667</v>
       </c>
       <c r="I30">
-        <v>2.101666666666667</v>
-      </c>
-      <c r="J30">
         <v>2.8241666666666663</v>
       </c>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:11">
       <c r="A31">
         <v>1979</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>9</v>
+      <c r="B31">
+        <v>3.5644743384505931E-7</v>
       </c>
       <c r="C31">
-        <v>3.5644743384505931E-7</v>
+        <v>1.3169666666640851E-8</v>
       </c>
       <c r="D31">
-        <v>1.3169666666640851E-8</v>
+        <v>1.3436666666666667E-8</v>
       </c>
       <c r="E31">
-        <v>1.3436666666666667E-8</v>
+        <v>365379.5</v>
       </c>
       <c r="F31">
-        <v>365379.5</v>
+        <v>47.993876753423578</v>
       </c>
       <c r="G31">
-        <v>47.993876753423578</v>
+        <v>6.8641666666666659</v>
       </c>
       <c r="H31">
-        <v>6.8641666666666659</v>
+        <v>2.3641666666666667</v>
       </c>
       <c r="I31">
-        <v>2.3641666666666667</v>
-      </c>
-      <c r="J31">
         <v>3.5091666666666668</v>
       </c>
     </row>
-    <row r="32" spans="1:12">
-      <c r="A32" s="4">
+    <row r="32" spans="1:11">
+      <c r="A32" s="3">
         <v>1980</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>9</v>
+      <c r="B32">
+        <v>7.1561895931028768E-7</v>
       </c>
       <c r="C32">
-        <v>7.1561895931028768E-7</v>
+        <v>1.83715833333225E-8</v>
       </c>
       <c r="D32">
-        <v>1.83715833333225E-8</v>
+        <v>1.8555833333333333E-8</v>
       </c>
       <c r="E32">
-        <v>1.8555833333333333E-8</v>
+        <v>371462.66146879323</v>
       </c>
       <c r="F32">
-        <v>371462.66146879323</v>
+        <v>61.133147907170674</v>
       </c>
       <c r="G32">
-        <v>61.133147907170674</v>
+        <v>6.7508333333333335</v>
       </c>
       <c r="H32">
-        <v>6.7508333333333335</v>
+        <v>2.7041666666666666</v>
       </c>
       <c r="I32">
-        <v>2.7041666666666666</v>
-      </c>
-      <c r="J32">
         <v>3.8825000000000003</v>
       </c>
-      <c r="L32">
+      <c r="K32">
         <v>96.413372499999994</v>
       </c>
     </row>
-    <row r="33" spans="1:12">
-      <c r="A33" s="4">
+    <row r="33" spans="1:11">
+      <c r="A33" s="3">
         <v>1981</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>9</v>
+      <c r="B33">
+        <v>1.4632734295504563E-6</v>
       </c>
       <c r="C33">
-        <v>1.4632734295504563E-6</v>
+        <v>4.4026916666672502E-8</v>
       </c>
       <c r="D33">
-        <v>4.4026916666672502E-8</v>
+        <v>6.0456666666666667E-8</v>
       </c>
       <c r="E33">
-        <v>6.0456666666666667E-8</v>
+        <v>351086.19772822899</v>
       </c>
       <c r="F33">
-        <v>351086.19772822899</v>
+        <v>64.403813775912027</v>
       </c>
       <c r="G33">
-        <v>64.403813775912027</v>
+        <v>6.9241666666666672</v>
       </c>
       <c r="H33">
-        <v>6.9241666666666672</v>
+        <v>2.9208333333333334</v>
       </c>
       <c r="I33">
-        <v>2.9208333333333334</v>
-      </c>
-      <c r="J33">
         <v>3.875</v>
       </c>
-      <c r="L33">
+      <c r="K33">
         <v>96.277270000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:12">
-      <c r="A34" s="4">
+    <row r="34" spans="1:11">
+      <c r="A34" s="3">
         <v>1982</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>9</v>
+      <c r="B34">
+        <v>3.8744467014732513E-6</v>
       </c>
       <c r="C34">
-        <v>3.8744467014732513E-6</v>
+        <v>2.5922533333326324E-7</v>
       </c>
       <c r="D34">
-        <v>2.5922533333326324E-7</v>
+        <v>2.6837083333333337E-7</v>
       </c>
       <c r="E34">
-        <v>2.6837083333333337E-7</v>
+        <v>341412.69038842875</v>
       </c>
       <c r="F34">
-        <v>341412.69038842875</v>
+        <v>63.108126912532697</v>
       </c>
       <c r="G34">
-        <v>63.108126912532697</v>
+        <v>5.7816666666666663</v>
       </c>
       <c r="H34">
-        <v>5.7816666666666663</v>
+        <v>2.3733333333333331</v>
       </c>
       <c r="I34">
-        <v>2.3733333333333331</v>
-      </c>
-      <c r="J34">
         <v>3.5216666666666665</v>
       </c>
-      <c r="L34">
+      <c r="K34">
         <v>95.983422500000003</v>
       </c>
     </row>
-    <row r="35" spans="1:12">
-      <c r="A35" s="4">
+    <row r="35" spans="1:11">
+      <c r="A35" s="3">
         <v>1983</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>9</v>
+      <c r="B35">
+        <v>1.7194789170759481E-5</v>
       </c>
       <c r="C35">
-        <v>1.7194789170759481E-5</v>
+        <v>1.0529957499584134E-6</v>
       </c>
       <c r="D35">
-        <v>1.0529957499584134E-6</v>
+        <v>1.1270083333333333E-6</v>
       </c>
       <c r="E35">
-        <v>1.1270083333333333E-6</v>
+        <v>356519.30333917926</v>
       </c>
       <c r="F35">
-        <v>356519.30333917926</v>
+        <v>60.77148773908003</v>
       </c>
       <c r="G35">
-        <v>60.77148773908003</v>
+        <v>6.7274999999999991</v>
       </c>
       <c r="H35">
-        <v>6.7274999999999991</v>
+        <v>2.9933333333333332</v>
       </c>
       <c r="I35">
-        <v>2.9933333333333332</v>
-      </c>
-      <c r="J35">
         <v>3.5833333333333335</v>
       </c>
-      <c r="L35">
+      <c r="K35">
         <v>96.24383499999999</v>
       </c>
     </row>
-    <row r="36" spans="1:12">
-      <c r="A36" s="4">
+    <row r="36" spans="1:11">
+      <c r="A36" s="3">
         <v>1984</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>9</v>
+      <c r="B36">
+        <v>1.2496025875645964E-4</v>
       </c>
       <c r="C36">
-        <v>1.2496025875645964E-4</v>
+        <v>6.7649116665999983E-6</v>
       </c>
       <c r="D36">
-        <v>6.7649116665999983E-6</v>
+        <v>7.4717166666666667E-6</v>
       </c>
       <c r="E36">
-        <v>7.4717166666666667E-6</v>
+        <v>363017.86020544503</v>
       </c>
       <c r="F36">
-        <v>363017.86020544503</v>
+        <v>61.815584920180775</v>
       </c>
       <c r="G36">
-        <v>61.815584920180775</v>
+        <v>7.0158333333333323</v>
       </c>
       <c r="H36">
-        <v>7.0158333333333323</v>
+        <v>3.0474999999999999</v>
       </c>
       <c r="I36">
-        <v>3.0474999999999999</v>
-      </c>
-      <c r="J36">
         <v>3.4624999999999999</v>
       </c>
-      <c r="L36">
+      <c r="K36">
         <v>96.171317500000015</v>
       </c>
     </row>
-    <row r="37" spans="1:12">
-      <c r="A37" s="4">
+    <row r="37" spans="1:11">
+      <c r="A37" s="3">
         <v>1985</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>9</v>
+      <c r="B37">
+        <v>9.6491974673538496E-4</v>
       </c>
       <c r="C37">
-        <v>9.6491974673538496E-4</v>
+        <v>6.0180899999999998E-5</v>
       </c>
       <c r="D37">
-        <v>6.0180899999999998E-5</v>
+        <v>6.243458333333333E-5</v>
       </c>
       <c r="E37">
-        <v>6.243458333333333E-5</v>
+        <v>336473.48621732229</v>
       </c>
       <c r="F37">
-        <v>336473.48621732229</v>
+        <v>60.296612213834919</v>
       </c>
       <c r="G37">
-        <v>60.296612213834919</v>
+        <v>5.4208333333333334</v>
       </c>
       <c r="H37">
-        <v>5.4208333333333334</v>
+        <v>2.4908333333333332</v>
       </c>
       <c r="I37">
-        <v>2.4908333333333332</v>
-      </c>
-      <c r="J37">
         <v>3.1966666666666668</v>
       </c>
-      <c r="L37">
+      <c r="K37">
         <v>95.669607499999984</v>
       </c>
     </row>
-    <row r="38" spans="1:12">
-      <c r="A38" s="4">
+    <row r="38" spans="1:11">
+      <c r="A38" s="3">
         <v>1986</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>9</v>
+      <c r="B38">
+        <v>1.83421967553058E-3</v>
       </c>
       <c r="C38">
-        <v>1.83421967553058E-3</v>
+        <v>9.4303166666666601E-5</v>
       </c>
       <c r="D38">
-        <v>9.4303166666666601E-5</v>
+        <v>9.638333333333335E-5</v>
       </c>
       <c r="E38">
-        <v>9.638333333333335E-5</v>
+        <v>361051.69326929824</v>
       </c>
       <c r="F38">
-        <v>361051.69326929824</v>
+        <v>58.324778079595077</v>
       </c>
       <c r="G38">
-        <v>58.324778079595077</v>
+        <v>5.0041666666666673</v>
       </c>
       <c r="H38">
-        <v>5.0041666666666673</v>
+        <v>1.9583333333333335</v>
       </c>
       <c r="I38">
-        <v>1.9583333333333335</v>
+        <v>2.7074999999999996</v>
       </c>
       <c r="J38">
-        <v>2.7074999999999996</v>
+        <v>75.365222282043248</v>
       </c>
       <c r="K38">
-        <v>75.365222282043248</v>
-      </c>
-      <c r="L38">
         <v>94.947552499999986</v>
       </c>
     </row>
-    <row r="39" spans="1:12">
-      <c r="A39" s="4">
+    <row r="39" spans="1:11">
+      <c r="A39" s="3">
         <v>1987</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>9</v>
+      <c r="B39">
+        <v>4.2431861037260125E-3</v>
       </c>
       <c r="C39">
-        <v>4.2431861037260125E-3</v>
+        <v>2.1442983333333325E-4</v>
       </c>
       <c r="D39">
-        <v>2.1442983333333325E-4</v>
+        <v>2.4051666666666667E-4</v>
       </c>
       <c r="E39">
-        <v>2.4051666666666667E-4</v>
+        <v>371274.36921824724</v>
       </c>
       <c r="F39">
-        <v>371274.36921824724</v>
+        <v>62.318764284832326</v>
       </c>
       <c r="G39">
-        <v>62.318764284832326</v>
+        <v>5.0750000000000002</v>
       </c>
       <c r="H39">
-        <v>5.0750000000000002</v>
+        <v>1.5566666666666669</v>
       </c>
       <c r="I39">
-        <v>1.5566666666666669</v>
+        <v>2.5525000000000002</v>
       </c>
       <c r="J39">
-        <v>2.5525000000000002</v>
+        <v>80.8186978131708</v>
       </c>
       <c r="K39">
-        <v>80.8186978131708</v>
-      </c>
-      <c r="L39">
         <v>94.848002500000007</v>
       </c>
     </row>
-    <row r="40" spans="1:12">
-      <c r="A40" s="4">
+    <row r="40" spans="1:11">
+      <c r="A40" s="3">
         <v>1988</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>9</v>
+      <c r="B40">
+        <v>1.8795355487814008E-2</v>
       </c>
       <c r="C40">
-        <v>1.8795355487814008E-2</v>
+        <v>8.7526041666666676E-4</v>
       </c>
       <c r="D40">
-        <v>8.7526041666666676E-4</v>
+        <v>1.1325833333333333E-3</v>
       </c>
       <c r="E40">
-        <v>1.1325833333333333E-3</v>
+        <v>363555.38836705271</v>
       </c>
       <c r="F40">
-        <v>363555.38836705271</v>
+        <v>65.764108869962186</v>
       </c>
       <c r="G40">
-        <v>65.764108869962186</v>
+        <v>7.2116666666666669</v>
       </c>
       <c r="H40">
-        <v>7.2116666666666669</v>
+        <v>2.273333333333333</v>
       </c>
       <c r="I40">
-        <v>2.273333333333333</v>
+        <v>3.3266666666666667</v>
       </c>
       <c r="J40">
-        <v>3.3266666666666667</v>
+        <v>87.105525469955495</v>
       </c>
       <c r="K40">
-        <v>87.105525469955495</v>
-      </c>
-      <c r="L40">
         <v>95.39542999999999</v>
       </c>
     </row>
-    <row r="41" spans="1:12">
-      <c r="A41" s="4">
+    <row r="41" spans="1:11">
+      <c r="A41" s="3">
         <v>1989</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>9</v>
+      <c r="B41">
+        <v>0.59758970527284472</v>
       </c>
       <c r="C41">
-        <v>0.59758970527284472</v>
+        <v>4.233396083333333E-2</v>
       </c>
       <c r="D41">
-        <v>4.233396083333333E-2</v>
+        <v>4.7387583333333337E-2</v>
       </c>
       <c r="E41">
-        <v>4.7387583333333337E-2</v>
+        <v>336975.48100512847</v>
       </c>
       <c r="F41">
-        <v>336975.48100512847</v>
+        <v>71.82016813835736</v>
       </c>
       <c r="G41">
-        <v>71.82016813835736</v>
+        <v>6.6333333333333329</v>
       </c>
       <c r="H41">
-        <v>6.6333333333333329</v>
+        <v>2.4341666666666666</v>
       </c>
       <c r="I41">
-        <v>2.4341666666666666</v>
+        <v>3.8758333333333335</v>
       </c>
       <c r="J41">
-        <v>3.8758333333333335</v>
+        <v>81.675626037251021</v>
       </c>
       <c r="K41">
-        <v>81.675626037251021</v>
-      </c>
-      <c r="L41">
         <v>95.21069</v>
       </c>
     </row>
-    <row r="42" spans="1:12">
-      <c r="A42" s="4">
+    <row r="42" spans="1:11">
+      <c r="A42" s="3">
         <v>1990</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>9</v>
+      <c r="B42">
+        <v>14.425593119413374</v>
       </c>
       <c r="C42">
-        <v>14.425593119413374</v>
+        <v>0.48758908333333351</v>
       </c>
       <c r="D42">
-        <v>0.48758908333333351</v>
+        <v>0.51120833333333338</v>
       </c>
       <c r="E42">
-        <v>0.51120833333333338</v>
+        <v>328135.14800146373</v>
       </c>
       <c r="F42">
-        <v>328135.14800146373</v>
+        <v>74.146165068363501</v>
       </c>
       <c r="G42">
-        <v>74.146165068363501</v>
+        <v>5.8224999999999998</v>
       </c>
       <c r="H42">
-        <v>5.8224999999999998</v>
+        <v>2.398333333333333</v>
       </c>
       <c r="I42">
-        <v>2.398333333333333</v>
+        <v>2.9808333333333334</v>
       </c>
       <c r="J42">
-        <v>2.9808333333333334</v>
+        <v>78.094344005312095</v>
       </c>
       <c r="K42">
-        <v>78.094344005312095</v>
-      </c>
-      <c r="L42">
         <v>94.883385000000004</v>
       </c>
     </row>
-    <row r="43" spans="1:12">
-      <c r="A43" s="4">
+    <row r="43" spans="1:11">
+      <c r="A43" s="3">
         <v>1991</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>9</v>
+      <c r="B43">
+        <v>39.190253982310935</v>
       </c>
       <c r="C43">
-        <v>39.190253982310935</v>
+        <v>0.95355441666666674</v>
       </c>
       <c r="D43">
-        <v>0.95355441666666674</v>
+        <v>0.98662499999999997</v>
       </c>
       <c r="E43">
-        <v>0.98662499999999997</v>
+        <v>361080.65464477526</v>
       </c>
       <c r="F43">
-        <v>361080.65464477526</v>
+        <v>74.196294312544651</v>
       </c>
       <c r="G43">
-        <v>74.196294312544651</v>
+        <v>5.5991666666666662</v>
       </c>
       <c r="H43">
-        <v>5.5991666666666662</v>
+        <v>2.3291666666666666</v>
       </c>
       <c r="I43">
-        <v>2.3291666666666666</v>
+        <v>2.7383333333333333</v>
       </c>
       <c r="J43">
-        <v>2.7383333333333333</v>
+        <v>78.569203321535298</v>
       </c>
       <c r="K43">
-        <v>78.569203321535298</v>
-      </c>
-      <c r="L43">
         <v>94.455277499999994</v>
       </c>
     </row>
-    <row r="44" spans="1:12">
-      <c r="A44" s="4">
+    <row r="44" spans="1:11">
+      <c r="A44" s="3">
         <v>1992</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>9</v>
+      <c r="B44">
+        <v>48.948607671209771</v>
       </c>
       <c r="C44">
-        <v>48.948607671209771</v>
+        <v>0.99064166666666653</v>
       </c>
       <c r="D44">
-        <v>0.99064166666666653</v>
+        <v>0.999</v>
       </c>
       <c r="E44">
+        <v>389367.35948664951</v>
+      </c>
+      <c r="F44">
+        <v>74.807755504436315</v>
+      </c>
+      <c r="G44">
+        <v>5.5708333333333329</v>
+      </c>
+      <c r="H44">
+        <v>2.2858333333333332</v>
+      </c>
+      <c r="I44">
+        <v>3.3824999999999998</v>
+      </c>
+      <c r="J44">
+        <v>83.792801255260997</v>
+      </c>
+      <c r="K44">
+        <v>94.481462499999992</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="3">
+        <v>1993</v>
+      </c>
+      <c r="B45">
+        <v>54.142795508475523</v>
+      </c>
+      <c r="C45">
+        <v>0.99894583333333353</v>
+      </c>
+      <c r="D45">
         <v>0.999</v>
       </c>
-      <c r="F44">
-        <v>389367.35948664951</v>
-      </c>
-      <c r="G44">
-        <v>74.807755504436315</v>
-      </c>
-      <c r="H44">
-        <v>5.5708333333333329</v>
-      </c>
-      <c r="I44">
-        <v>2.2858333333333332</v>
-      </c>
-      <c r="J44">
-        <v>3.3824999999999998</v>
-      </c>
-      <c r="K44">
-        <v>83.792801255260997</v>
-      </c>
-      <c r="L44">
-        <v>94.481462499999992</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12">
-      <c r="A45" s="4">
-        <v>1993</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C45">
-        <v>54.142795508475523</v>
-      </c>
-      <c r="D45">
-        <v>0.99894583333333353</v>
-      </c>
       <c r="E45">
+        <v>410740.39264327125</v>
+      </c>
+      <c r="F45">
+        <v>74.636871508379798</v>
+      </c>
+      <c r="G45">
+        <v>6.0441666666666665</v>
+      </c>
+      <c r="H45">
+        <v>2.2166666666666668</v>
+      </c>
+      <c r="I45">
+        <v>3.2058333333333335</v>
+      </c>
+      <c r="J45">
+        <v>83.524236149406917</v>
+      </c>
+      <c r="K45">
+        <v>94.589710000000011</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" s="3">
+        <v>1994</v>
+      </c>
+      <c r="B46">
+        <v>56.404522868788511</v>
+      </c>
+      <c r="C46">
+        <v>0.9990083333333335</v>
+      </c>
+      <c r="D46">
         <v>0.999</v>
       </c>
-      <c r="F45">
-        <v>410740.39264327125</v>
-      </c>
-      <c r="G45">
-        <v>74.636871508379798</v>
-      </c>
-      <c r="H45">
-        <v>6.0441666666666665</v>
-      </c>
-      <c r="I45">
-        <v>2.2166666666666668</v>
-      </c>
-      <c r="J45">
-        <v>3.2058333333333335</v>
-      </c>
-      <c r="K45">
-        <v>83.524236149406917</v>
-      </c>
-      <c r="L45">
-        <v>94.589710000000011</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12">
-      <c r="A46" s="4">
-        <v>1994</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C46">
-        <v>56.404522868788511</v>
-      </c>
-      <c r="D46">
-        <v>0.9990083333333335</v>
-      </c>
       <c r="E46">
+        <v>434504.71145245375</v>
+      </c>
+      <c r="F46">
+        <v>75.892211633256579</v>
+      </c>
+      <c r="G46">
+        <v>6.1049999999999995</v>
+      </c>
+      <c r="H46">
+        <v>2.4091666666666667</v>
+      </c>
+      <c r="I46">
+        <v>3.5158333333333331</v>
+      </c>
+      <c r="J46">
+        <v>84.100556633629154</v>
+      </c>
+      <c r="K46">
+        <v>94.630064999999988</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="3">
+        <v>1995</v>
+      </c>
+      <c r="B47">
+        <v>58.308795145157085</v>
+      </c>
+      <c r="C47">
+        <v>0.99975000000000003</v>
+      </c>
+      <c r="D47">
         <v>0.999</v>
       </c>
-      <c r="F46">
-        <v>434504.71145245375</v>
-      </c>
-      <c r="G46">
-        <v>75.892211633256579</v>
-      </c>
-      <c r="H46">
-        <v>6.1049999999999995</v>
-      </c>
-      <c r="I46">
-        <v>2.4091666666666667</v>
-      </c>
-      <c r="J46">
-        <v>3.5158333333333331</v>
-      </c>
-      <c r="K46">
-        <v>84.100556633629154</v>
-      </c>
-      <c r="L46">
-        <v>94.630064999999988</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12">
-      <c r="A47" s="4">
-        <v>1995</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C47">
-        <v>58.308795145157085</v>
-      </c>
-      <c r="D47">
-        <v>0.99975000000000003</v>
-      </c>
       <c r="E47">
+        <v>422140.86608689453</v>
+      </c>
+      <c r="F47">
+        <v>79.316464015773832</v>
+      </c>
+      <c r="G47">
+        <v>5.8500000000000005</v>
+      </c>
+      <c r="H47">
+        <v>2.5575000000000001</v>
+      </c>
+      <c r="I47">
+        <v>4.0925000000000002</v>
+      </c>
+      <c r="J47">
+        <v>87.936584516628329</v>
+      </c>
+      <c r="K47">
+        <v>94.552227500000015</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" s="3">
+        <v>1996</v>
+      </c>
+      <c r="B48">
+        <v>58.39956900536707</v>
+      </c>
+      <c r="C48">
+        <v>0.99966250000000012</v>
+      </c>
+      <c r="D48">
         <v>0.999</v>
       </c>
-      <c r="F47">
-        <v>422140.86608689453</v>
-      </c>
-      <c r="G47">
-        <v>79.316464015773832</v>
-      </c>
-      <c r="H47">
-        <v>5.8500000000000005</v>
-      </c>
-      <c r="I47">
-        <v>2.5575000000000001</v>
-      </c>
-      <c r="J47">
-        <v>4.0925000000000002</v>
-      </c>
-      <c r="K47">
-        <v>87.936584516628329</v>
-      </c>
-      <c r="L47">
-        <v>94.552227500000015</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12">
-      <c r="A48" s="4">
-        <v>1996</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C48">
-        <v>58.39956900536707</v>
-      </c>
-      <c r="D48">
-        <v>0.99966250000000012</v>
-      </c>
       <c r="E48">
+        <v>444970.048953166</v>
+      </c>
+      <c r="F48">
+        <v>80.118304304962095</v>
+      </c>
+      <c r="G48">
+        <v>7.2741666666666669</v>
+      </c>
+      <c r="H48">
+        <v>3.5516666666666667</v>
+      </c>
+      <c r="I48">
+        <v>4.7666666666666666</v>
+      </c>
+      <c r="J48">
+        <v>91.89573546418994</v>
+      </c>
+      <c r="K48">
+        <v>94.737285</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" s="3">
+        <v>1997</v>
+      </c>
+      <c r="B49">
+        <v>58.708261967207271</v>
+      </c>
+      <c r="C49">
+        <v>0.99950000000000006</v>
+      </c>
+      <c r="D49">
         <v>0.999</v>
       </c>
-      <c r="F48">
-        <v>444970.048953166</v>
-      </c>
-      <c r="G48">
-        <v>80.118304304962095</v>
-      </c>
-      <c r="H48">
-        <v>7.2741666666666669</v>
-      </c>
-      <c r="I48">
-        <v>3.5516666666666667</v>
-      </c>
-      <c r="J48">
-        <v>4.7666666666666666</v>
-      </c>
-      <c r="K48">
-        <v>91.89573546418994</v>
-      </c>
-      <c r="L48">
-        <v>94.737285</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12">
-      <c r="A49" s="4">
-        <v>1997</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C49">
-        <v>58.708261967207271</v>
-      </c>
-      <c r="D49">
+      <c r="E49">
+        <v>480613.35555235855</v>
+      </c>
+      <c r="F49">
+        <v>78.146565888925323</v>
+      </c>
+      <c r="G49">
+        <v>7.4025000000000007</v>
+      </c>
+      <c r="H49">
+        <v>2.5991666666666666</v>
+      </c>
+      <c r="I49">
+        <v>3.7124999999999999</v>
+      </c>
+      <c r="J49">
+        <v>90.011005203540648</v>
+      </c>
+      <c r="K49">
+        <v>94.685770000000005</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="3">
+        <v>1998</v>
+      </c>
+      <c r="B50">
+        <v>59.2511169204219</v>
+      </c>
+      <c r="C50">
         <v>0.99950000000000006</v>
       </c>
-      <c r="E49">
+      <c r="D50">
         <v>0.999</v>
       </c>
-      <c r="F49">
-        <v>480613.35555235855</v>
-      </c>
-      <c r="G49">
-        <v>78.146565888925323</v>
-      </c>
-      <c r="H49">
-        <v>7.4025000000000007</v>
-      </c>
-      <c r="I49">
-        <v>2.5991666666666666</v>
-      </c>
-      <c r="J49">
-        <v>3.7124999999999999</v>
-      </c>
-      <c r="K49">
-        <v>90.011005203540648</v>
-      </c>
-      <c r="L49">
-        <v>94.685770000000005</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12">
-      <c r="A50" s="4">
-        <v>1998</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C50">
-        <v>59.2511169204219</v>
-      </c>
-      <c r="D50">
+      <c r="E50">
+        <v>498898.49389205227</v>
+      </c>
+      <c r="F50">
+        <v>73.434111074597411</v>
+      </c>
+      <c r="G50">
+        <v>5.9249999999999998</v>
+      </c>
+      <c r="H50">
+        <v>2.2041666666666666</v>
+      </c>
+      <c r="I50">
+        <v>2.9033333333333333</v>
+      </c>
+      <c r="J50">
+        <v>84.894782173615027</v>
+      </c>
+      <c r="K50">
+        <v>94.179695000000009</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" s="3">
+        <v>1999</v>
+      </c>
+      <c r="B51">
+        <v>58.559847795516582</v>
+      </c>
+      <c r="C51">
         <v>0.99950000000000006</v>
       </c>
-      <c r="E50">
+      <c r="D51">
         <v>0.999</v>
       </c>
-      <c r="F50">
-        <v>498898.49389205227</v>
-      </c>
-      <c r="G50">
-        <v>73.434111074597411</v>
-      </c>
-      <c r="H50">
-        <v>5.9249999999999998</v>
-      </c>
-      <c r="I50">
-        <v>2.2041666666666666</v>
-      </c>
-      <c r="J50">
-        <v>2.9033333333333333</v>
-      </c>
-      <c r="K50">
-        <v>84.894782173615027</v>
-      </c>
-      <c r="L50">
-        <v>94.179695000000009</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12">
-      <c r="A51" s="4">
-        <v>1999</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C51">
-        <v>58.559847795516582</v>
-      </c>
-      <c r="D51">
+      <c r="E51">
+        <v>482075.70485385729</v>
+      </c>
+      <c r="F51">
+        <v>74.065067367729142</v>
+      </c>
+      <c r="G51">
+        <v>4.5674999999999999</v>
+      </c>
+      <c r="H51">
+        <v>1.885</v>
+      </c>
+      <c r="I51">
+        <v>2.5758333333333336</v>
+      </c>
+      <c r="J51">
+        <v>79.209357616395422</v>
+      </c>
+      <c r="K51">
+        <v>93.897237500000003</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B52">
+        <v>58.00990792958757</v>
+      </c>
+      <c r="C52">
         <v>0.99950000000000006</v>
       </c>
-      <c r="E51">
+      <c r="D52">
         <v>0.999</v>
       </c>
-      <c r="F51">
-        <v>482075.70485385729</v>
-      </c>
-      <c r="G51">
-        <v>74.065067367729142</v>
-      </c>
-      <c r="H51">
-        <v>4.5674999999999999</v>
-      </c>
-      <c r="I51">
-        <v>1.885</v>
-      </c>
-      <c r="J51">
-        <v>2.5758333333333336</v>
-      </c>
-      <c r="K51">
-        <v>79.209357616395422</v>
-      </c>
-      <c r="L51">
-        <v>93.897237500000003</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12">
-      <c r="A52" s="4">
-        <v>2000</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C52">
-        <v>58.00990792958757</v>
-      </c>
-      <c r="D52">
+      <c r="E52">
+        <v>478821.98360656225</v>
+      </c>
+      <c r="F52">
+        <v>78.869536641472166</v>
+      </c>
+      <c r="G52">
+        <v>4.7324999999999999</v>
+      </c>
+      <c r="H52">
+        <v>1.8591666666666666</v>
+      </c>
+      <c r="I52">
+        <v>2.5683333333333334</v>
+      </c>
+      <c r="J52">
+        <v>86.409850768956446</v>
+      </c>
+      <c r="K52">
+        <v>94.262552499999998</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" s="3">
+        <v>2001</v>
+      </c>
+      <c r="B53">
+        <v>57.391810372093261</v>
+      </c>
+      <c r="C53">
         <v>0.99950000000000006</v>
       </c>
-      <c r="E52">
+      <c r="D53">
         <v>0.999</v>
       </c>
-      <c r="F52">
-        <v>478821.98360656225</v>
-      </c>
-      <c r="G52">
-        <v>78.869536641472166</v>
-      </c>
-      <c r="H52">
-        <v>4.7324999999999999</v>
-      </c>
-      <c r="I52">
-        <v>1.8591666666666666</v>
-      </c>
-      <c r="J52">
-        <v>2.5683333333333334</v>
-      </c>
-      <c r="K52">
-        <v>86.409850768956446</v>
-      </c>
-      <c r="L52">
-        <v>94.262552499999998</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12">
-      <c r="A53" s="4">
-        <v>2001</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C53">
-        <v>57.391810372093261</v>
-      </c>
-      <c r="D53">
-        <v>0.99950000000000006</v>
-      </c>
       <c r="E53">
-        <v>0.999</v>
+        <v>458143.83278938604</v>
       </c>
       <c r="F53">
-        <v>458143.83278938604</v>
+        <v>76.07624055208673</v>
       </c>
       <c r="G53">
-        <v>76.07624055208673</v>
+        <v>4.43</v>
       </c>
       <c r="H53">
-        <v>4.43</v>
+        <v>1.8933333333333333</v>
       </c>
       <c r="I53">
-        <v>1.8933333333333333</v>
+        <v>2.8299999999999996</v>
       </c>
       <c r="J53">
-        <v>2.8299999999999996</v>
+        <v>84.962486747441631</v>
       </c>
       <c r="K53">
-        <v>84.962486747441631</v>
-      </c>
-      <c r="L53">
         <v>94.241612500000002</v>
       </c>
     </row>
-    <row r="54" spans="1:12">
-      <c r="A54" s="4">
+    <row r="54" spans="1:11">
+      <c r="A54" s="3">
         <v>2002</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>9</v>
+      <c r="B54">
+        <v>72.238237362113338</v>
       </c>
       <c r="C54">
-        <v>72.238237362113338</v>
+        <v>3.063256666666665</v>
       </c>
       <c r="D54">
-        <v>3.063256666666665</v>
+        <v>3.1985833333333336</v>
       </c>
       <c r="E54">
-        <v>3.1985833333333336</v>
+        <v>408315.564630304</v>
       </c>
       <c r="F54">
-        <v>408315.564630304</v>
+        <v>74.196516595464928</v>
       </c>
       <c r="G54">
-        <v>74.196516595464928</v>
+        <v>4.9333333333333336</v>
       </c>
       <c r="H54">
-        <v>4.9333333333333336</v>
+        <v>2.1308333333333329</v>
       </c>
       <c r="I54">
-        <v>2.1308333333333329</v>
+        <v>3.4058333333333337</v>
       </c>
       <c r="J54">
-        <v>3.4058333333333337</v>
+        <v>86.256194369742317</v>
       </c>
       <c r="K54">
-        <v>86.256194369742317</v>
-      </c>
-      <c r="L54">
         <v>94.661415000000005</v>
       </c>
     </row>
-    <row r="55" spans="1:12">
-      <c r="A55" s="4">
+    <row r="55" spans="1:11">
+      <c r="A55" s="3">
         <v>2003</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>9</v>
+      <c r="B55">
+        <v>81.949327212066052</v>
       </c>
       <c r="C55">
-        <v>81.949327212066052</v>
+        <v>2.9006291666666675</v>
       </c>
       <c r="D55">
-        <v>2.9006291666666675</v>
+        <v>2.9463166666666667</v>
       </c>
       <c r="E55">
-        <v>2.9463166666666667</v>
+        <v>446064.22675398202</v>
       </c>
       <c r="F55">
-        <v>446064.22675398202</v>
+        <v>76.385146237265829</v>
       </c>
       <c r="G55">
-        <v>76.385146237265829</v>
+        <v>6.0841666666666665</v>
       </c>
       <c r="H55">
-        <v>6.0841666666666665</v>
+        <v>2.2675000000000001</v>
       </c>
       <c r="I55">
-        <v>2.2675000000000001</v>
+        <v>3.4449999999999998</v>
       </c>
       <c r="J55">
-        <v>3.4449999999999998</v>
+        <v>93.690435507014442</v>
       </c>
       <c r="K55">
-        <v>93.690435507014442</v>
-      </c>
-      <c r="L55">
         <v>95.094934999999992</v>
       </c>
     </row>
-    <row r="56" spans="1:12">
-      <c r="A56" s="4">
+    <row r="56" spans="1:11">
+      <c r="A56" s="3">
         <v>2004</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>9</v>
+      <c r="B56">
+        <v>85.56819803775592</v>
       </c>
       <c r="C56">
-        <v>85.56819803775592</v>
+        <v>2.9233008189033174</v>
       </c>
       <c r="D56">
-        <v>2.9233008189033174</v>
+        <v>2.9461666666666666</v>
       </c>
       <c r="E56">
-        <v>2.9461666666666666</v>
+        <v>485227.57736949652</v>
       </c>
       <c r="F56">
-        <v>485227.57736949652</v>
+        <v>80.69010844561285</v>
       </c>
       <c r="G56">
-        <v>80.69010844561285</v>
+        <v>7.5549999999999997</v>
       </c>
       <c r="H56">
-        <v>7.5549999999999997</v>
+        <v>2.4649999999999999</v>
       </c>
       <c r="I56">
-        <v>2.4649999999999999</v>
+        <v>3.5683333333333334</v>
       </c>
       <c r="J56">
-        <v>3.5683333333333334</v>
+        <v>100.19489663791815</v>
       </c>
       <c r="K56">
-        <v>100.19489663791815</v>
-      </c>
-      <c r="L56">
         <v>95.516995000000009</v>
       </c>
     </row>
-    <row r="57" spans="1:12">
-      <c r="A57" s="4">
+    <row r="57" spans="1:11">
+      <c r="A57" s="3">
         <v>2005</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>9</v>
+      <c r="B57">
+        <v>93.819024425056625</v>
       </c>
       <c r="C57">
-        <v>93.819024425056625</v>
+        <v>2.9036575</v>
       </c>
       <c r="D57">
-        <v>2.9036575</v>
+        <v>2.9312333333333331</v>
       </c>
       <c r="E57">
-        <v>2.9312333333333331</v>
+        <v>527486.03617352003</v>
       </c>
       <c r="F57">
-        <v>527486.03617352003</v>
+        <v>86.749917844232627</v>
       </c>
       <c r="G57">
-        <v>86.749917844232627</v>
+        <v>5.9500000000000011</v>
       </c>
       <c r="H57">
-        <v>5.9500000000000011</v>
+        <v>1.9641666666666666</v>
       </c>
       <c r="I57">
-        <v>1.9641666666666666</v>
+        <v>3.3591666666666673</v>
       </c>
       <c r="J57">
-        <v>3.3591666666666673</v>
+        <v>97.004906397511647</v>
       </c>
       <c r="K57">
-        <v>97.004906397511647</v>
-      </c>
-      <c r="L57">
         <v>95.972000000000008</v>
       </c>
     </row>
-    <row r="58" spans="1:12">
-      <c r="A58" s="4">
+    <row r="58" spans="1:11">
+      <c r="A58" s="3">
         <v>2006</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>9</v>
+      <c r="B58">
+        <v>104.04195841625601</v>
       </c>
       <c r="C58">
-        <v>104.04195841625601</v>
+        <v>3.0543133333333348</v>
       </c>
       <c r="D58">
-        <v>3.0543133333333348</v>
+        <v>3.0784250000000002</v>
       </c>
       <c r="E58">
-        <v>3.0784250000000002</v>
+        <v>570206.27825144096</v>
       </c>
       <c r="F58">
-        <v>570206.27825144096</v>
+        <v>90.976010515938171</v>
       </c>
       <c r="G58">
-        <v>90.976010515938171</v>
+        <v>5.6483333333333325</v>
       </c>
       <c r="H58">
-        <v>5.6483333333333325</v>
+        <v>2.2808333333333333</v>
       </c>
       <c r="I58">
-        <v>2.2808333333333333</v>
+        <v>4.0333333333333332</v>
       </c>
       <c r="J58">
-        <v>4.0333333333333332</v>
+        <v>101.34372071092852</v>
       </c>
       <c r="K58">
-        <v>101.34372071092852</v>
-      </c>
-      <c r="L58">
         <v>96.712327500000015</v>
       </c>
     </row>
-    <row r="59" spans="1:12">
-      <c r="A59" s="4">
+    <row r="59" spans="1:11">
+      <c r="A59" s="3">
         <v>2007</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>9</v>
+      <c r="B59">
+        <v>122.60767576677668</v>
       </c>
       <c r="C59">
-        <v>122.60767576677668</v>
+        <v>3.0956488492063499</v>
       </c>
       <c r="D59">
-        <v>3.0956488492063499</v>
+        <v>3.1195666666666666</v>
       </c>
       <c r="E59">
-        <v>3.1195666666666666</v>
+        <v>621387.37253883295</v>
       </c>
       <c r="F59">
-        <v>621387.37253883295</v>
+        <v>94.814327965823168</v>
       </c>
       <c r="G59">
-        <v>94.814327965823168</v>
+        <v>7.7424999999999997</v>
       </c>
       <c r="H59">
-        <v>7.7424999999999997</v>
+        <v>3.3908333333333336</v>
       </c>
       <c r="I59">
-        <v>3.3908333333333336</v>
+        <v>5.7591666666666663</v>
       </c>
       <c r="J59">
-        <v>5.7591666666666663</v>
+        <v>107.40892527282151</v>
       </c>
       <c r="K59">
-        <v>107.40892527282151</v>
-      </c>
-      <c r="L59">
         <v>98.393617500000005</v>
       </c>
     </row>
-    <row r="60" spans="1:12">
-      <c r="A60" s="4">
+    <row r="60" spans="1:11">
+      <c r="A60" s="3">
         <v>2008</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>9</v>
+      <c r="B60">
+        <v>155.78550583817082</v>
       </c>
       <c r="C60">
-        <v>155.78550583817082</v>
+        <v>3.1441645598845573</v>
       </c>
       <c r="D60">
-        <v>3.1441645598845573</v>
+        <v>3.1797</v>
       </c>
       <c r="E60">
-        <v>3.1797</v>
+        <v>646556.03089785669</v>
       </c>
       <c r="F60">
-        <v>646556.03089785669</v>
+        <v>105.72461386789327</v>
       </c>
       <c r="G60">
-        <v>105.72461386789327</v>
+        <v>11.310833333333333</v>
       </c>
       <c r="H60">
-        <v>11.310833333333333</v>
+        <v>4.7799999999999994</v>
       </c>
       <c r="I60">
-        <v>4.7799999999999994</v>
+        <v>8.019166666666667</v>
       </c>
       <c r="J60">
-        <v>8.019166666666667</v>
+        <v>120.73117029835501</v>
       </c>
       <c r="K60">
-        <v>120.73117029835501</v>
-      </c>
-      <c r="L60">
         <v>100.33704</v>
       </c>
     </row>
-    <row r="61" spans="1:12">
-      <c r="A61" s="4">
+    <row r="61" spans="1:11">
+      <c r="A61" s="3">
         <v>2009</v>
       </c>
-      <c r="B61" s="3" t="s">
-        <v>9</v>
+      <c r="B61">
+        <v>178.5084453826374</v>
       </c>
       <c r="C61">
-        <v>178.5084453826374</v>
+        <v>3.7101068305232774</v>
       </c>
       <c r="D61">
-        <v>3.7101068305232774</v>
+        <v>3.7477999999999998</v>
       </c>
       <c r="E61">
-        <v>3.7477999999999998</v>
+        <v>609306.81353967823</v>
       </c>
       <c r="F61">
-        <v>609306.81353967823</v>
+        <v>93.572132763719978</v>
       </c>
       <c r="G61">
-        <v>93.572132763719978</v>
+        <v>10.0525</v>
       </c>
       <c r="H61">
-        <v>10.0525</v>
+        <v>3.7449999999999997</v>
       </c>
       <c r="I61">
-        <v>3.7449999999999997</v>
+        <v>5.3041666666666663</v>
       </c>
       <c r="J61">
-        <v>5.3041666666666663</v>
+        <v>121.49359600613475</v>
       </c>
       <c r="K61">
-        <v>121.49359600613475</v>
-      </c>
-      <c r="L61">
         <v>97.694755000000001</v>
       </c>
     </row>
-    <row r="62" spans="1:12">
-      <c r="A62" s="4">
+    <row r="62" spans="1:11">
+      <c r="A62" s="3">
         <v>2010</v>
       </c>
-      <c r="B62" s="3" t="s">
-        <v>9</v>
+      <c r="B62">
+        <v>219.7253050710828</v>
       </c>
       <c r="C62">
-        <v>219.7253050710828</v>
+        <v>3.8962951544704976</v>
       </c>
       <c r="D62">
-        <v>3.8962951544704976</v>
+        <v>3.9225500000000002</v>
       </c>
       <c r="E62">
-        <v>3.9225500000000002</v>
+        <v>669907.66780942515</v>
       </c>
       <c r="F62">
-        <v>669907.66780942515</v>
+        <v>100.00000000000009</v>
       </c>
       <c r="G62">
-        <v>100.00000000000009</v>
+        <v>9.9741666666666671</v>
       </c>
       <c r="H62">
-        <v>9.9741666666666671</v>
+        <v>3.8308333333333335</v>
       </c>
       <c r="I62">
-        <v>3.8308333333333335</v>
+        <v>5.1150000000000002</v>
       </c>
       <c r="J62">
-        <v>5.1150000000000002</v>
+        <v>125.83870834436911</v>
       </c>
       <c r="K62">
-        <v>125.83870834436911</v>
-      </c>
-      <c r="L62">
         <v>98.449952499999995</v>
       </c>
     </row>
-    <row r="63" spans="1:12">
-      <c r="A63" s="4">
+    <row r="63" spans="1:11">
+      <c r="A63" s="3">
         <v>2011</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>9</v>
+      <c r="B63">
+        <v>271.21628884862417</v>
       </c>
       <c r="C63">
-        <v>271.21628884862417</v>
+        <v>4.1101395762132631</v>
       </c>
       <c r="D63">
-        <v>4.1101395762132631</v>
+        <v>4.1441583333333334</v>
       </c>
       <c r="E63">
-        <v>4.1441583333333334</v>
+        <v>710408.39829484804</v>
       </c>
       <c r="F63">
-        <v>710408.39829484804</v>
+        <v>110.90371344068376</v>
       </c>
       <c r="G63">
-        <v>110.90371344068376</v>
+        <v>12.524999999999999</v>
       </c>
       <c r="H63">
-        <v>12.524999999999999</v>
+        <v>6.015833333333334</v>
       </c>
       <c r="I63">
-        <v>6.015833333333334</v>
+        <v>7.4366666666666674</v>
       </c>
       <c r="J63">
-        <v>7.4366666666666674</v>
+        <v>138.8648388426916</v>
       </c>
       <c r="K63">
-        <v>138.8648388426916</v>
-      </c>
-      <c r="L63">
         <v>100.08649750000001</v>
       </c>
     </row>
-    <row r="64" spans="1:12">
-      <c r="A64" s="4">
+    <row r="64" spans="1:11">
+      <c r="A64" s="3">
         <v>2012</v>
       </c>
-      <c r="B64" s="3" t="s">
-        <v>9</v>
+      <c r="B64">
+        <v>335.36971461385974</v>
       </c>
       <c r="C64">
-        <v>335.36971461385974</v>
+        <v>4.5369343601874554</v>
       </c>
       <c r="D64">
-        <v>4.5369343601874554</v>
+        <v>4.5759499999999997</v>
       </c>
       <c r="E64">
-        <v>4.5759499999999997</v>
+        <v>704014.44333909312</v>
       </c>
       <c r="F64">
-        <v>704014.44333909312</v>
+        <v>111.21261912586274</v>
       </c>
       <c r="G64">
-        <v>111.21261912586274</v>
+        <v>13.958333333333334</v>
       </c>
       <c r="H64">
-        <v>13.958333333333334</v>
+        <v>6.6725000000000003</v>
       </c>
       <c r="I64">
-        <v>6.6725000000000003</v>
+        <v>7.5983333333333327</v>
       </c>
       <c r="J64">
-        <v>7.5983333333333327</v>
+        <v>144.71742987903173</v>
       </c>
       <c r="K64">
-        <v>144.71742987903173</v>
-      </c>
-      <c r="L64">
         <v>100.34992249999999</v>
       </c>
     </row>
-    <row r="65" spans="1:12">
-      <c r="A65" s="4">
+    <row r="65" spans="1:11">
+      <c r="A65" s="3">
         <v>2013</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>9</v>
+      <c r="B65">
+        <v>420.91792328681294</v>
       </c>
       <c r="C65">
-        <v>420.91792328681294</v>
+        <v>5.4593526646570378</v>
       </c>
       <c r="D65">
-        <v>5.4593526646570378</v>
+        <v>5.5442150000000003</v>
       </c>
       <c r="E65">
-        <v>5.5442150000000003</v>
+        <v>720476.20900330553</v>
       </c>
       <c r="F65">
-        <v>720476.20900330553</v>
+        <v>109.99014130791974</v>
       </c>
       <c r="G65">
-        <v>109.99014130791974</v>
+        <v>14.066666666666666</v>
       </c>
       <c r="H65">
+        <v>6.1541666666666659</v>
+      </c>
+      <c r="I65">
+        <v>7.315833333333333</v>
+      </c>
+      <c r="J65">
+        <v>135.34683833803825</v>
+      </c>
+      <c r="K65">
+        <v>100.20165</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66" s="3">
+        <v>2014</v>
+      </c>
+      <c r="B66">
+        <v>577.91942212497088</v>
+      </c>
+      <c r="C66">
+        <v>8.0752759928133386</v>
+      </c>
+      <c r="D66">
+        <v>8.2313666666666663</v>
+      </c>
+      <c r="E66">
+        <v>702662.87609203579</v>
+      </c>
+      <c r="F66">
+        <v>108.807098258298</v>
+      </c>
+      <c r="G66">
+        <v>12.4725</v>
+      </c>
+      <c r="H66">
+        <v>4.1124999999999998</v>
+      </c>
+      <c r="I66">
+        <v>6.3333333333333339</v>
+      </c>
+      <c r="J66">
+        <v>132.40057768259095</v>
+      </c>
+      <c r="K66">
+        <v>99.664657500000004</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
+      <c r="A67" s="3">
+        <v>2015</v>
+      </c>
+      <c r="B67">
+        <v>715.13182608233808</v>
+      </c>
+      <c r="C67">
+        <v>9.2331855247242842</v>
+      </c>
+      <c r="D67">
+        <v>9.4420833333333327</v>
+      </c>
+      <c r="E67">
+        <v>721476.20868965599</v>
+      </c>
+      <c r="F67">
+        <v>97.739073282944503</v>
+      </c>
+      <c r="G67">
+        <v>9.4891666666666676</v>
+      </c>
+      <c r="H67">
+        <v>3.7058333333333335</v>
+      </c>
+      <c r="I67">
+        <v>5.2758333333333338</v>
+      </c>
+      <c r="J67">
+        <v>126.53532208892406</v>
+      </c>
+      <c r="K67">
+        <v>99.108935000000002</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
+      <c r="A68" s="3">
+        <v>2016</v>
+      </c>
+      <c r="B68">
+        <v>1002.8487072668606</v>
+      </c>
+      <c r="C68">
+        <v>14.758175087339575</v>
+      </c>
+      <c r="D68">
+        <v>14.944875</v>
+      </c>
+      <c r="E68">
+        <v>708666.76663170452</v>
+      </c>
+      <c r="F68">
+        <v>94.485704896483796</v>
+      </c>
+      <c r="G68">
+        <v>9.3916666666666657</v>
+      </c>
+      <c r="H68">
+        <v>3.4783333333333335</v>
+      </c>
+      <c r="I68">
+        <v>4.1091666666666669</v>
+      </c>
+      <c r="J68">
+        <v>134.1115549441098</v>
+      </c>
+      <c r="K68">
+        <v>99.523349999999994</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69" s="3">
+        <v>2017</v>
+      </c>
+      <c r="B69">
+        <v>1259.3535939785834</v>
+      </c>
+      <c r="C69">
+        <v>16.562706925141125</v>
+      </c>
+      <c r="D69">
+        <v>16.758258333333334</v>
+      </c>
+      <c r="E69">
+        <v>728601.09571029758</v>
+      </c>
+      <c r="F69">
+        <v>97.226421294774923</v>
+      </c>
+      <c r="G69">
+        <v>9.3908333333333331</v>
+      </c>
+      <c r="H69">
+        <v>3.3591666666666669</v>
+      </c>
+      <c r="I69">
+        <v>4.4366666666666674</v>
+      </c>
+      <c r="J69">
+        <v>130.32916347172841</v>
+      </c>
+      <c r="K69">
+        <v>99.388580000000005</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70" s="3">
+        <v>2018</v>
+      </c>
+      <c r="B70">
+        <v>1691.0250427255914</v>
+      </c>
+      <c r="C70">
+        <v>28.094991666666651</v>
+      </c>
+      <c r="D70">
+        <v>29.31688333333333</v>
+      </c>
+      <c r="E70">
+        <v>707377.25</v>
+      </c>
+      <c r="F70">
+        <v>100.26947091685859</v>
+      </c>
+      <c r="G70">
+        <v>9.1508333333333329</v>
+      </c>
+      <c r="H70">
+        <v>3.4683333333333333</v>
+      </c>
+      <c r="I70">
+        <v>5.1433333333333326</v>
+      </c>
+      <c r="J70">
+        <v>131.75766971058712</v>
+      </c>
+      <c r="K70">
+        <v>99.136635000000012</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71" s="3">
+        <v>2019</v>
+      </c>
+      <c r="B71">
+        <v>2596.5402792260552</v>
+      </c>
+      <c r="C71">
+        <v>48.147891666666673</v>
+      </c>
+      <c r="D71">
+        <v>49.225200000000008</v>
+      </c>
+      <c r="E71">
+        <v>693046.25</v>
+      </c>
+      <c r="F71">
+        <v>98.994413407821256</v>
+      </c>
+      <c r="G71">
+        <v>8.427500000000002</v>
+      </c>
+      <c r="H71">
+        <v>3.753333333333333</v>
+      </c>
+      <c r="I71">
+        <v>4.7433333333333332</v>
+      </c>
+      <c r="J71">
+        <v>130.75229333720949</v>
+      </c>
+      <c r="K71">
+        <v>99.155389999999997</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72" s="3">
+        <v>2020</v>
+      </c>
+      <c r="B72">
+        <v>3687.4791374441456</v>
+      </c>
+      <c r="C72">
+        <v>70.539166666666659</v>
+      </c>
+      <c r="D72">
+        <v>71.605741666666674</v>
+      </c>
+      <c r="E72">
+        <v>624591.25</v>
+      </c>
+      <c r="F72">
+        <v>96.523167926388467</v>
+      </c>
+      <c r="G72">
+        <v>8.9841666666666669</v>
+      </c>
+      <c r="H72">
+        <v>3.5008333333333335</v>
+      </c>
+      <c r="I72">
+        <v>4.8574999999999999</v>
+      </c>
+      <c r="J72">
+        <v>131.4404485</v>
+      </c>
+      <c r="K72">
+        <v>99.781077067057282</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73" s="4">
+        <v>2021</v>
+      </c>
+      <c r="B73">
+        <v>5472.5648748265339</v>
+      </c>
+      <c r="C73">
+        <v>94.99074166666658</v>
+      </c>
+      <c r="D73">
+        <v>95.80361666666667</v>
+      </c>
+      <c r="E73">
+        <v>689810</v>
+      </c>
+      <c r="F73">
+        <v>105.060795267828</v>
+      </c>
+      <c r="G73">
+        <v>13.041666666666666</v>
+      </c>
+      <c r="H73">
+        <v>5.3966666666666665</v>
+      </c>
+      <c r="I73">
+        <v>6.84</v>
+      </c>
+      <c r="J73">
+        <v>144.07327574999999</v>
+      </c>
+      <c r="K73">
+        <v>100.06425984700515</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74" s="4">
+        <v>2022</v>
+      </c>
+      <c r="B74">
+        <v>9436.3850700839084</v>
+      </c>
+      <c r="C74">
+        <v>130.61655000000025</v>
+      </c>
+      <c r="D74">
+        <v>133.55472499999999</v>
+      </c>
+      <c r="E74">
+        <v>726162</v>
+      </c>
+      <c r="F74">
+        <v>113.95333552415376</v>
+      </c>
+      <c r="G74">
+        <v>14.85</v>
+      </c>
+      <c r="H74">
+        <v>6.7575000000000003</v>
+      </c>
+      <c r="I74">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J74">
+        <v>144.87243674999999</v>
+      </c>
+      <c r="K74">
+        <v>99.729338963826464</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
+      <c r="A75" s="4">
+        <v>2023</v>
+      </c>
+      <c r="B75">
+        <v>22032.915058706552</v>
+      </c>
+      <c r="C75">
+        <v>296.25804166666677</v>
+      </c>
+      <c r="D75">
+        <v>317.15970833333336</v>
+      </c>
+      <c r="E75">
+        <v>714463.5</v>
+      </c>
+      <c r="F75">
+        <v>110.43049622083474</v>
+      </c>
+      <c r="G75">
         <v>14.066666666666666</v>
       </c>
-      <c r="I65">
-        <v>6.1541666666666659</v>
-      </c>
-      <c r="J65">
-        <v>7.315833333333333</v>
-      </c>
-      <c r="K65">
-        <v>135.34683833803825</v>
-      </c>
-      <c r="L65">
-        <v>100.20165</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12">
-      <c r="A66" s="4">
-        <v>2014</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C66">
-        <v>577.91942212497088</v>
-      </c>
-      <c r="D66">
-        <v>8.0752759928133386</v>
-      </c>
-      <c r="E66">
-        <v>8.2313666666666663</v>
-      </c>
-      <c r="F66">
-        <v>702662.87609203579</v>
-      </c>
-      <c r="G66">
-        <v>108.807098258298</v>
-      </c>
-      <c r="H66">
-        <v>12.4725</v>
-      </c>
-      <c r="I66">
-        <v>4.1124999999999998</v>
-      </c>
-      <c r="J66">
-        <v>6.3333333333333339</v>
-      </c>
-      <c r="K66">
-        <v>132.40057768259095</v>
-      </c>
-      <c r="L66">
-        <v>99.664657500000004</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12">
-      <c r="A67" s="4">
-        <v>2015</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C67">
-        <v>715.13182608233808</v>
-      </c>
-      <c r="D67">
-        <v>9.2331855247242842</v>
-      </c>
-      <c r="E67">
-        <v>9.4420833333333327</v>
-      </c>
-      <c r="F67">
-        <v>721476.20868965599</v>
-      </c>
-      <c r="G67">
-        <v>97.739073282944503</v>
-      </c>
-      <c r="H67">
-        <v>9.4891666666666676</v>
-      </c>
-      <c r="I67">
-        <v>3.7058333333333335</v>
-      </c>
-      <c r="J67">
-        <v>5.2758333333333338</v>
-      </c>
-      <c r="K67">
-        <v>126.53532208892406</v>
-      </c>
-      <c r="L67">
-        <v>99.108935000000002</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12">
-      <c r="A68" s="4">
-        <v>2016</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C68">
-        <v>1002.8487072668606</v>
-      </c>
-      <c r="D68">
-        <v>14.758175087339575</v>
-      </c>
-      <c r="E68">
-        <v>14.944875</v>
-      </c>
-      <c r="F68">
-        <v>708666.76663170452</v>
-      </c>
-      <c r="G68">
-        <v>94.485704896483796</v>
-      </c>
-      <c r="H68">
-        <v>9.3916666666666657</v>
-      </c>
-      <c r="I68">
-        <v>3.4783333333333335</v>
-      </c>
-      <c r="J68">
-        <v>4.1091666666666669</v>
-      </c>
-      <c r="K68">
-        <v>134.1115549441098</v>
-      </c>
-      <c r="L68">
-        <v>99.523349999999994</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12">
-      <c r="A69" s="4">
-        <v>2017</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C69">
-        <v>1259.3535939785834</v>
-      </c>
-      <c r="D69">
-        <v>16.562706925141125</v>
-      </c>
-      <c r="E69">
-        <v>16.758258333333334</v>
-      </c>
-      <c r="F69">
-        <v>728601.09571029758</v>
-      </c>
-      <c r="G69">
-        <v>97.226421294774923</v>
-      </c>
-      <c r="H69">
-        <v>9.3908333333333331</v>
-      </c>
-      <c r="I69">
-        <v>3.3591666666666669</v>
-      </c>
-      <c r="J69">
-        <v>4.4366666666666674</v>
-      </c>
-      <c r="K69">
-        <v>130.32916347172841</v>
-      </c>
-      <c r="L69">
-        <v>99.388580000000005</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12">
-      <c r="A70" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C70">
-        <v>1691.0250427255914</v>
-      </c>
-      <c r="D70">
-        <v>28.094991666666651</v>
-      </c>
-      <c r="E70">
-        <v>29.31688333333333</v>
-      </c>
-      <c r="F70">
-        <v>707377.25</v>
-      </c>
-      <c r="G70">
-        <v>100.26947091685859</v>
-      </c>
-      <c r="H70">
-        <v>9.1508333333333329</v>
-      </c>
-      <c r="I70">
-        <v>3.4683333333333333</v>
-      </c>
-      <c r="J70">
-        <v>5.1433333333333326</v>
-      </c>
-      <c r="K70">
-        <v>131.75766971058712</v>
-      </c>
-      <c r="L70">
-        <v>99.136635000000012</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12">
-      <c r="A71" s="4">
-        <v>2019</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C71">
-        <v>2596.5402792260552</v>
-      </c>
-      <c r="D71">
-        <v>48.147891666666673</v>
-      </c>
-      <c r="E71">
-        <v>49.225200000000008</v>
-      </c>
-      <c r="F71">
-        <v>693046.25</v>
-      </c>
-      <c r="G71">
-        <v>98.994413407821256</v>
-      </c>
-      <c r="H71">
-        <v>8.427500000000002</v>
-      </c>
-      <c r="I71">
-        <v>3.753333333333333</v>
-      </c>
-      <c r="J71">
-        <v>4.7433333333333332</v>
-      </c>
-      <c r="K71">
-        <v>130.75229333720949</v>
-      </c>
-      <c r="L71">
-        <v>99.155389999999997</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12">
-      <c r="A72" s="4">
-        <v>2020</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C72">
-        <v>3687.4791374441456</v>
-      </c>
-      <c r="D72">
-        <v>70.539166666666659</v>
-      </c>
-      <c r="E72">
-        <v>71.605741666666674</v>
-      </c>
-      <c r="F72">
-        <v>624591.25</v>
-      </c>
-      <c r="G72">
-        <v>96.523167926388467</v>
-      </c>
-      <c r="H72">
-        <v>8.9841666666666669</v>
-      </c>
-      <c r="I72">
-        <v>3.5008333333333335</v>
-      </c>
-      <c r="J72">
-        <v>4.8574999999999999</v>
-      </c>
-      <c r="K72">
-        <v>131.4404485</v>
-      </c>
-      <c r="L72">
-        <v>99.781077067057282</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12">
-      <c r="A73" s="5">
-        <v>2021</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C73">
-        <v>5472.5648748265339</v>
-      </c>
-      <c r="D73">
-        <v>94.99074166666658</v>
-      </c>
-      <c r="E73">
-        <v>95.80361666666667</v>
-      </c>
-      <c r="F73">
-        <v>689810</v>
-      </c>
-      <c r="G73">
-        <v>105.060795267828</v>
-      </c>
-      <c r="H73">
-        <v>13.041666666666666</v>
-      </c>
-      <c r="I73">
-        <v>5.3966666666666665</v>
-      </c>
-      <c r="J73">
-        <v>6.84</v>
-      </c>
-      <c r="K73">
-        <v>144.07327574999999</v>
-      </c>
-      <c r="L73">
-        <v>100.06425984700515</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12">
-      <c r="A74" s="5">
-        <v>2022</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C74">
-        <v>9436.3850700839084</v>
-      </c>
-      <c r="D74">
-        <v>130.61655000000025</v>
-      </c>
-      <c r="E74">
-        <v>133.55472499999999</v>
-      </c>
-      <c r="F74">
-        <v>726162</v>
-      </c>
-      <c r="G74">
-        <v>113.95333552415376</v>
-      </c>
-      <c r="H74">
-        <v>14.85</v>
-      </c>
-      <c r="I74">
-        <v>6.7575000000000003</v>
-      </c>
-      <c r="J74">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="K74">
-        <v>144.87243674999999</v>
-      </c>
-      <c r="L74">
-        <v>99.729338963826464</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12">
-      <c r="A75" s="5">
-        <v>2023</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C75">
-        <v>22032.915058706552</v>
-      </c>
-      <c r="D75">
-        <v>296.25804166666677</v>
-      </c>
-      <c r="E75">
-        <v>317.15970833333336</v>
-      </c>
-      <c r="F75">
-        <v>714463.5</v>
-      </c>
-      <c r="G75">
-        <v>110.43049622083474</v>
-      </c>
       <c r="H75">
-        <v>14.066666666666666</v>
+        <v>5.9491666666666667</v>
       </c>
       <c r="I75">
-        <v>5.9491666666666667</v>
+        <v>7.6691666666666674</v>
       </c>
       <c r="J75">
-        <v>7.6691666666666674</v>
+        <v>138.42204950000001</v>
       </c>
       <c r="K75">
-        <v>138.42204950000001</v>
-      </c>
-      <c r="L75">
         <v>100.06328328450525</v>
       </c>
     </row>
-    <row r="76" spans="1:12">
-      <c r="A76" s="5"/>
-      <c r="B76" s="3"/>
-    </row>
-    <row r="77" spans="1:12">
-      <c r="A77" s="5"/>
-      <c r="B77" s="3"/>
-    </row>
-    <row r="78" spans="1:12">
-      <c r="A78" s="5"/>
-      <c r="B78" s="3"/>
-    </row>
-    <row r="79" spans="1:12">
-      <c r="A79" s="5"/>
-      <c r="B79" s="3"/>
-    </row>
-    <row r="80" spans="1:12">
+    <row r="76" spans="1:11">
+      <c r="A76" s="4"/>
+    </row>
+    <row r="77" spans="1:11">
+      <c r="A77" s="4"/>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78" s="4"/>
+    </row>
+    <row r="79" spans="1:11">
+      <c r="A79" s="4"/>
+    </row>
+    <row r="80" spans="1:11">
       <c r="A80" s="1"/>
     </row>
     <row r="81" spans="1:1">

--- a/data/Data trimestral 1950 a 2023 PRUEBA (promedios anuales).xlsx
+++ b/data/Data trimestral 1950 a 2023 PRUEBA (promedios anuales).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mariana/Library/CloudStorage/GoogleDrive-marianabarrenadrive@gmail.com/Mi unidad/TESIS UCA/UCA Proyecto de TESIS/Estadísticas/Github/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89035412-09C7-C641-A336-A999D967B02D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A96DA41A-3C98-F34B-999D-76C6105DD5E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17180" xr2:uid="{081104FB-1F73-C945-9C9A-B52E522B90FE}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{081104FB-1F73-C945-9C9A-B52E522B90FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -498,6 +498,9 @@
       <c r="E2">
         <v>142105.75</v>
       </c>
+      <c r="F2">
+        <v>11.880783392461481</v>
+      </c>
       <c r="G2">
         <v>2.4458333333333333</v>
       </c>
@@ -524,6 +527,9 @@
       <c r="E3">
         <v>147447.5</v>
       </c>
+      <c r="F3">
+        <v>14.94600098597579</v>
+      </c>
       <c r="G3">
         <v>2.8908333333333336</v>
       </c>
@@ -550,6 +556,9 @@
       <c r="E4">
         <v>140518</v>
       </c>
+      <c r="F4">
+        <v>14.149044411662073</v>
+      </c>
       <c r="G4">
         <v>2.8233333333333328</v>
       </c>
@@ -576,6 +585,9 @@
       <c r="E5">
         <v>147325</v>
       </c>
+      <c r="F5">
+        <v>13.568696547290031</v>
+      </c>
       <c r="G5">
         <v>2.6141666666666672</v>
       </c>
@@ -602,6 +614,9 @@
       <c r="E6">
         <v>153323.75</v>
       </c>
+      <c r="F6">
+        <v>13.850696565893344</v>
+      </c>
       <c r="G6">
         <v>3.039166666666667</v>
       </c>
@@ -628,6 +643,9 @@
       <c r="E7">
         <v>163917.75</v>
       </c>
+      <c r="F7">
+        <v>13.813913954771177</v>
+      </c>
       <c r="G7">
         <v>2.2925</v>
       </c>
@@ -653,6 +671,9 @@
       </c>
       <c r="E8">
         <v>168624.5</v>
+      </c>
+      <c r="F8">
+        <v>14.128609627705313</v>
       </c>
       <c r="G8">
         <v>2.3983333333333334</v>
